--- a/artfynd/A 52303-2020 artfynd.xlsx
+++ b/artfynd/A 52303-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122941102</v>
       </c>
       <c r="B2" t="n">
-        <v>96890</v>
+        <v>96898</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52303-2020 artfynd.xlsx
+++ b/artfynd/A 52303-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122941102</v>
       </c>
       <c r="B2" t="n">
-        <v>96898</v>
+        <v>96901</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52303-2020 artfynd.xlsx
+++ b/artfynd/A 52303-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122941102</v>
       </c>
       <c r="B2" t="n">
-        <v>96901</v>
+        <v>96903</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52303-2020 artfynd.xlsx
+++ b/artfynd/A 52303-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122941102</v>
       </c>
       <c r="B2" t="n">
-        <v>96903</v>
+        <v>96909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 52303-2020 artfynd.xlsx
+++ b/artfynd/A 52303-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122941102</v>
       </c>
       <c r="B2" t="n">
-        <v>96912</v>
+        <v>96929</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
